--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JOSE_LEONARDO_ORTIZ</t>
+          <t>JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>001 VIRGEN MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.75754</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.83256</v>
-      </c>
-      <c r="I2" t="n">
-        <v>351</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.75754</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.83256</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>11011 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.76264</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.8359</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1636</v>
-      </c>
-      <c r="J3" t="n">
-        <v>53</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.76264</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.8359</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>10008</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.759729</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.838713</v>
-      </c>
-      <c r="I4" t="n">
-        <v>739</v>
-      </c>
-      <c r="J4" t="n">
-        <v>36</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.759729</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.838713</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>10011 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.75778</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.84457</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1074</v>
-      </c>
-      <c r="J5" t="n">
-        <v>41</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.75778</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.84457</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>10797 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.75895</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.8301</v>
-      </c>
-      <c r="I6" t="n">
-        <v>667</v>
-      </c>
-      <c r="J6" t="n">
-        <v>43</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.75895</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.8301</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>10823 JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.75121</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.83695</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1217</v>
-      </c>
-      <c r="J7" t="n">
-        <v>65</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.75121</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.83695</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>10826 CARLOS CASTAÑEDA IPARRAGUIRRE</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.75183</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.84222</v>
-      </c>
-      <c r="I8" t="n">
-        <v>574</v>
-      </c>
-      <c r="J8" t="n">
-        <v>34</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.75183</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.84222</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>10834 SANTA ANA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.74994</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.84831</v>
-      </c>
-      <c r="I9" t="n">
-        <v>775</v>
-      </c>
-      <c r="J9" t="n">
-        <v>38</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.74994</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.84831</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>10836 LA APLICACION</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.76233</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.83551</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1509</v>
-      </c>
-      <c r="J10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.76233</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.83551</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1509</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>10878 PEDRO PABLO ATUSPARIAS / PEDRO PABLO ATUSPARIAS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.7594</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.82804</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1110</v>
-      </c>
-      <c r="J11" t="n">
-        <v>47</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.7594</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.82804</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>10924</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.75908</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.84701</v>
-      </c>
-      <c r="I12" t="n">
-        <v>425</v>
-      </c>
-      <c r="J12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.75908</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.84701</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>10945 HEROINA MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.75686</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.82344000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>584</v>
-      </c>
-      <c r="J13" t="n">
-        <v>26</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.75686</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.82344</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>11009 VIRGEN DE LA MEDALLA MILAGROSA / 11009 VIRGEN MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.75891</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.83855</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1609</v>
-      </c>
-      <c r="J14" t="n">
-        <v>74</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.75891</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.83855</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>11010 MARIANO MELGAR VALDIVIESO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-6.75194</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.83127</v>
-      </c>
-      <c r="I15" t="n">
-        <v>682</v>
-      </c>
-      <c r="J15" t="n">
-        <v>28</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.75194</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.83127</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>11057 SAN LORENZO</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-6.75241</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.84958</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2126</v>
-      </c>
-      <c r="J16" t="n">
-        <v>79</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-6.75241</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.84958</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2126</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>CRISTO REY</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-6.750357</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.839156</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1478</v>
-      </c>
-      <c r="J17" t="n">
-        <v>84</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-6.750357</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.839156</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>NICOLAS LA TORRE</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-6.76267</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.83483</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1435</v>
-      </c>
-      <c r="J18" t="n">
-        <v>69</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-6.76267</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.83483</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>SANTA CECILIA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-6.75923</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.83676</v>
-      </c>
-      <c r="I19" t="n">
-        <v>275</v>
-      </c>
-      <c r="J19" t="n">
-        <v>18</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-6.75923</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.83676</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-6.7477</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.84971</v>
-      </c>
-      <c r="I20" t="n">
-        <v>327</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-6.7477</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.84971</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>11587 YEHUDE SIMONS MUNARO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-6.75151</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-79.82015</v>
-      </c>
-      <c r="I21" t="n">
-        <v>497</v>
-      </c>
-      <c r="J21" t="n">
-        <v>19</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-6.75151</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.82015</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>ELIEL SCHOOL</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-6.75692</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-79.85536999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>459</v>
-      </c>
-      <c r="J22" t="n">
-        <v>18</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-6.75692</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.85537</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>PARAISO SCHOOL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-6.755874</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-79.848</v>
-      </c>
-      <c r="I23" t="n">
-        <v>443</v>
-      </c>
-      <c r="J23" t="n">
-        <v>24</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-6.755874</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.848</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>ALBERT EINSTEIN COLLEGE</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-6.74425</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-79.83320999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>203</v>
-      </c>
-      <c r="J24" t="n">
-        <v>10</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-6.74425</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-79.83321</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>11584 ESCUELA CONCERTADA SOLARIS</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-6.745478</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-79.835196</v>
-      </c>
-      <c r="I25" t="n">
-        <v>531</v>
-      </c>
-      <c r="J25" t="n">
-        <v>27</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-6.745478</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-79.835196</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>CRAYOLAS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-6.75845</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-79.83385</v>
-      </c>
-      <c r="I26" t="n">
-        <v>218</v>
-      </c>
-      <c r="J26" t="n">
-        <v>8</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-6.75845</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-79.83385</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>EL MAESTRO SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-6.7504</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-79.84576</v>
-      </c>
-      <c r="I27" t="n">
-        <v>212</v>
-      </c>
-      <c r="J27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-6.7504</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-79.84576</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-6.75565</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-79.84044</v>
-      </c>
-      <c r="I28" t="n">
-        <v>224</v>
-      </c>
-      <c r="J28" t="n">
-        <v>12</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-6.75565</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-79.84044</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>014 ESTRELLITAS DE MARIA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-6.762305</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-79.83592899999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>307</v>
-      </c>
-      <c r="J29" t="n">
-        <v>13</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-6.762305</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-79.835929</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>MARIANO MELGAR VALDIVIEZO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-6.75238</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-79.83177999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>659</v>
-      </c>
-      <c r="J30" t="n">
-        <v>32</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-6.75238</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-79.83178</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>318 VILLA KIDS</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-6.75172</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-79.81941999999999</v>
-      </c>
-      <c r="I31" t="n">
-        <v>234</v>
-      </c>
-      <c r="J31" t="n">
-        <v>8</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-6.75172</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-79.81942</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>LA ANUNCIATA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-6.74096</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-79.83394</v>
-      </c>
-      <c r="I32" t="n">
-        <v>938</v>
-      </c>
-      <c r="J32" t="n">
-        <v>34</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-6.74096</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-79.83394</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>UNICIENCIA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-6.75327</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-79.8546</v>
-      </c>
-      <c r="I33" t="n">
-        <v>206</v>
-      </c>
-      <c r="J33" t="n">
-        <v>14</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-6.75327</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-79.8546</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>CORAZON DE BELEN</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-6.744562</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-79.837219</v>
-      </c>
-      <c r="I34" t="n">
-        <v>571</v>
-      </c>
-      <c r="J34" t="n">
-        <v>16</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-6.744562</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-79.837219</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>SAN MIGUEL</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-6.74334</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-79.84177</v>
-      </c>
-      <c r="I35" t="n">
-        <v>335</v>
-      </c>
-      <c r="J35" t="n">
-        <v>15</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-6.74334</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-79.84177</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>278494</t>
+          <t>532452</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>001 VIRGEN MARIA AUXILIADORA</t>
+          <t>ALBERT EINSTEIN COLLEGE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.75754</t>
+          <t>-6.74425</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.83256</t>
+          <t>-79.83321</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>278516</t>
+          <t>673201</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11011 SEÑOR DE LOS MILAGROS</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.76264</t>
+          <t>-6.75565</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.8359</t>
+          <t>-79.84044</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>278578</t>
+          <t>673338</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>014 ESTRELLITAS DE MARIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.759729</t>
+          <t>-6.762305</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.838713</t>
+          <t>-79.835929</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>278601</t>
+          <t>278494</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10011 FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>001 VIRGEN MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.75778</t>
+          <t>-6.75754</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.84457</t>
+          <t>-79.83256</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>278615</t>
+          <t>737104</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10797 MICAELA BASTIDAS</t>
+          <t>UNICIENCIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.75895</t>
+          <t>-6.75327</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.8301</t>
+          <t>-79.8546</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>278620</t>
+          <t>819901</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10823 JOSE LEONARDO ORTIZ</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.75121</t>
+          <t>-6.74334</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.83695</t>
+          <t>-79.84177</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>278639</t>
+          <t>784096</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10826 CARLOS CASTAÑEDA IPARRAGUIRRE</t>
+          <t>CORAZON DE BELEN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.75183</t>
+          <t>-6.744562</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.84222</t>
+          <t>-79.837219</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>571</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>278644</t>
+          <t>278762</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10834 SANTA ANA</t>
+          <t>SANTA CECILIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.74994</t>
+          <t>-6.75923</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.84831</t>
+          <t>-79.83676</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>278658</t>
+          <t>513811</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10836 LA APLICACION</t>
+          <t>ELIEL SCHOOL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.76233</t>
+          <t>-6.75692</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.83551</t>
+          <t>-79.85537</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>459</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>278663</t>
+          <t>465711</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10878 PEDRO PABLO ATUSPARIAS / PEDRO PABLO ATUSPARIAS</t>
+          <t>11587 YEHUDE SIMONS MUNARO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.7594</t>
+          <t>-6.75151</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.82804</t>
+          <t>-79.82015</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>497</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>278696</t>
+          <t>278823</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10945 HEROINA MARIA PARADO DE BELLIDO</t>
+          <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.75686</t>
+          <t>-6.7477</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.82344</t>
+          <t>-79.84971</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>278700</t>
+          <t>520760</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11009 VIRGEN DE LA MEDALLA MILAGROSA / 11009 VIRGEN MEDALLA MILAGROSA</t>
+          <t>PARAISO SCHOOL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.75891</t>
+          <t>-6.755874</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.83855</t>
+          <t>-79.848</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>278719</t>
+          <t>278696</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11010 MARIANO MELGAR VALDIVIESO</t>
+          <t>10945 HEROINA MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.75194</t>
+          <t>-6.75686</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.83127</t>
+          <t>-79.82344</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>584</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>278724</t>
+          <t>554019</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11057 SAN LORENZO</t>
+          <t>11584 ESCUELA CONCERTADA SOLARIS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.75241</t>
+          <t>-6.745478</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.84958</t>
+          <t>-79.835196</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>531</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>278738</t>
+          <t>278719</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>11010 MARIANO MELGAR VALDIVIESO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.750357</t>
+          <t>-6.75194</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.839156</t>
+          <t>-79.83127</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>682</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>278743</t>
+          <t>673705</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NICOLAS LA TORRE</t>
+          <t>MARIANO MELGAR VALDIVIEZO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.76267</t>
+          <t>-6.75238</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.83483</t>
+          <t>-79.83178</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>659</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>278762</t>
+          <t>278639</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SANTA CECILIA</t>
+          <t>10826 CARLOS CASTAÑEDA IPARRAGUIRRE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.75923</t>
+          <t>-6.75183</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.83676</t>
+          <t>-79.84222</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>574</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>278823</t>
+          <t>674823</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HORACIO ZEVALLOS GAMEZ</t>
+          <t>LA ANUNCIATA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.7477</t>
+          <t>-6.74096</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.84971</t>
+          <t>-79.83394</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>938</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>465711</t>
+          <t>278578</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11587 YEHUDE SIMONS MUNARO</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.75151</t>
+          <t>-6.759729</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.82015</t>
+          <t>-79.838713</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>739</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>513811</t>
+          <t>278644</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ELIEL SCHOOL</t>
+          <t>10834 SANTA ANA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.75692</t>
+          <t>-6.74994</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.85537</t>
+          <t>-79.84831</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>775</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>520760</t>
+          <t>278601</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PARAISO SCHOOL</t>
+          <t>10011 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.755874</t>
+          <t>-6.75778</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.848</t>
+          <t>-79.84457</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>532452</t>
+          <t>278615</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN COLLEGE</t>
+          <t>10797 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.74425</t>
+          <t>-6.75895</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.83321</t>
+          <t>-79.8301</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>667</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>554019</t>
+          <t>278663</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11584 ESCUELA CONCERTADA SOLARIS</t>
+          <t>10878 PEDRO PABLO ATUSPARIAS / PEDRO PABLO ATUSPARIAS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.745478</t>
+          <t>-6.7594</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.835196</t>
+          <t>-79.82804</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>557876</t>
+          <t>278516</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CRAYOLAS</t>
+          <t>11011 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.75845</t>
+          <t>-6.76264</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.83385</t>
+          <t>-79.8359</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>576766</t>
+          <t>278658</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EL MAESTRO SAN FRANCISCO DE ASIS</t>
+          <t>10836 LA APLICACION</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.7504</t>
+          <t>-6.76233</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.84576</t>
+          <t>-79.83551</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>673201</t>
+          <t>278620</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>10823 JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.75565</t>
+          <t>-6.75121</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.84044</t>
+          <t>-79.83695</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>673338</t>
+          <t>278743</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>014 ESTRELLITAS DE MARIA</t>
+          <t>NICOLAS LA TORRE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.762305</t>
+          <t>-6.76267</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.835929</t>
+          <t>-79.83483</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>673705</t>
+          <t>576766</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR VALDIVIEZO</t>
+          <t>EL MAESTRO SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.75238</t>
+          <t>-6.7504</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.83178</t>
+          <t>-79.84576</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>674093</t>
+          <t>278700</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>318 VILLA KIDS</t>
+          <t>11009 VIRGEN DE LA MEDALLA MILAGROSA / 11009 VIRGEN MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.75172</t>
+          <t>-6.75891</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-79.81942</t>
+          <t>-79.83855</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>674823</t>
+          <t>278724</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LA ANUNCIATA</t>
+          <t>11057 SAN LORENZO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-6.74096</t>
+          <t>-6.75241</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.83394</t>
+          <t>-79.84958</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>737104</t>
+          <t>557876</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNICIENCIA</t>
+          <t>CRAYOLAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.75327</t>
+          <t>-6.75845</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.8546</t>
+          <t>-79.83385</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>784096</t>
+          <t>674093</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CORAZON DE BELEN</t>
+          <t>318 VILLA KIDS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.744562</t>
+          <t>-6.75172</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.837219</t>
+          <t>-79.81942</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>819901</t>
+          <t>278738</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.74334</t>
+          <t>-6.750357</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.84177</t>
+          <t>-79.839156</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">

--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>532452</t>
+          <t>819901</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN COLLEGE</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.74425</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.83321</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-6.74334</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.84177</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>673201</t>
+          <t>784096</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAGRADA FAMILIA</t>
+          <t>CORAZON DE BELEN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.75565</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.84044</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-6.744562</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-79.837219</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>673338</t>
+          <t>737104</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>014 ESTRELLITAS DE MARIA</t>
+          <t>UNICIENCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.762305</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.835929</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-6.75327</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.8546</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>278494</t>
+          <t>674823</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>001 VIRGEN MARIA AUXILIADORA</t>
+          <t>LA ANUNCIATA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.75754</t>
+          <t>938</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.83256</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-6.74096</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.83394</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>737104</t>
+          <t>674093</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UNICIENCIA</t>
+          <t>318 VILLA KIDS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.75327</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.8546</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-6.75172</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.81942</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>819901</t>
+          <t>673705</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>MARIANO MELGAR VALDIVIEZO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.74334</t>
+          <t>659</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.84177</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>-6.75238</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.83178</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>784096</t>
+          <t>673338</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CORAZON DE BELEN</t>
+          <t>014 ESTRELLITAS DE MARIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.744562</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.837219</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>-6.762305</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.835929</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>278762</t>
+          <t>673201</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SANTA CECILIA</t>
+          <t>SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.75923</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.83676</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-6.75565</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.84044</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>513811</t>
+          <t>576766</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ELIEL SCHOOL</t>
+          <t>EL MAESTRO SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.75692</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.85537</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>-6.7504</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.84576</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>465711</t>
+          <t>557876</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11587 YEHUDE SIMONS MUNARO</t>
+          <t>CRAYOLAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.75151</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.82015</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>-6.75845</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.83385</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>278682</t>
+          <t>554019</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11584 ESCUELA CONCERTADA SOLARIS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.75908</t>
+          <t>531</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.84701</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>-6.745478</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.835196</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>278823</t>
+          <t>532452</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HORACIO ZEVALLOS GAMEZ</t>
+          <t>ALBERT EINSTEIN COLLEGE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.7477</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.84971</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-6.74425</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.83321</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>-6.755874</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-79.848</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>278696</t>
+          <t>513811</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10945 HEROINA MARIA PARADO DE BELLIDO</t>
+          <t>ELIEL SCHOOL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.75686</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.82344</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>-6.75692</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.85537</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>554019</t>
+          <t>465711</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11584 ESCUELA CONCERTADA SOLARIS</t>
+          <t>11587 YEHUDE SIMONS MUNARO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.745478</t>
+          <t>497</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.835196</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>-6.75151</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.82015</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>278719</t>
+          <t>278823</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11010 MARIANO MELGAR VALDIVIESO</t>
+          <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.75194</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.83127</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>-6.7477</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-79.84971</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>673705</t>
+          <t>278762</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR VALDIVIEZO</t>
+          <t>SANTA CECILIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.75238</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.83178</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>-6.75923</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-79.83676</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>278639</t>
+          <t>278743</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10826 CARLOS CASTAÑEDA IPARRAGUIRRE</t>
+          <t>NICOLAS LA TORRE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.75183</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.84222</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>-6.76267</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-79.83483</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>674823</t>
+          <t>278738</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LA ANUNCIATA</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.74096</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.83394</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>-6.750357</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-79.839156</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>278578</t>
+          <t>278724</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>11057 SAN LORENZO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.759729</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.838713</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>-6.75241</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-79.84958</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>278644</t>
+          <t>278719</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10834 SANTA ANA</t>
+          <t>11010 MARIANO MELGAR VALDIVIESO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.74994</t>
+          <t>682</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.84831</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>-6.75194</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.83127</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>278601</t>
+          <t>278700</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10011 FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>11009 VIRGEN DE LA MEDALLA MILAGROSA / 11009 VIRGEN MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.75778</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.84457</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>-6.75891</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-79.83855</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>278615</t>
+          <t>278696</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10797 MICAELA BASTIDAS</t>
+          <t>10945 HEROINA MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.75895</t>
+          <t>584</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.8301</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>-6.75686</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-79.82344</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>278663</t>
+          <t>278682</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10878 PEDRO PABLO ATUSPARIAS / PEDRO PABLO ATUSPARIAS</t>
+          <t>10924</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.7594</t>
+          <t>425</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.82804</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>-6.75908</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-79.84701</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>278516</t>
+          <t>278663</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11011 SEÑOR DE LOS MILAGROS</t>
+          <t>10878 PEDRO PABLO ATUSPARIAS / PEDRO PABLO ATUSPARIAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.76264</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.8359</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>-6.7594</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-79.82804</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>1509</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>-6.76233</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-79.83551</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1509</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>278620</t>
+          <t>278644</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10823 JOSE LEONARDO ORTIZ</t>
+          <t>10834 SANTA ANA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.75121</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.83695</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>-6.74994</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-79.84831</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>278743</t>
+          <t>278639</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NICOLAS LA TORRE</t>
+          <t>10826 CARLOS CASTAÑEDA IPARRAGUIRRE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.76267</t>
+          <t>574</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.83483</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>-6.75183</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-79.84222</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>576766</t>
+          <t>278620</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EL MAESTRO SAN FRANCISCO DE ASIS</t>
+          <t>10823 JOSE LEONARDO ORTIZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.7504</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.84576</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-6.75121</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-79.83695</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>278700</t>
+          <t>278615</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11009 VIRGEN DE LA MEDALLA MILAGROSA / 11009 VIRGEN MEDALLA MILAGROSA</t>
+          <t>10797 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.75891</t>
+          <t>667</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-79.83855</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>-6.75895</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-79.8301</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>278724</t>
+          <t>278601</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>11057 SAN LORENZO</t>
+          <t>10011 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-6.75241</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.84958</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>-6.75778</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-79.84457</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>557876</t>
+          <t>278578</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CRAYOLAS</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.75845</t>
+          <t>739</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.83385</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-6.759729</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.838713</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>674093</t>
+          <t>278516</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>318 VILLA KIDS</t>
+          <t>11011 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.75172</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.81942</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-6.76264</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.8359</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>278738</t>
+          <t>278494</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>001 VIRGEN MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.750357</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.839156</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>-6.75754</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>-79.83256</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">

--- a/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
+++ b/ZonasEscolares/excels/LAMBAYEQUE-CHICLAYO-JOSE_LEONARDO_ORTIZ.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
